--- a/02_Zero_Shot/outputs/NLI/BART-large-MNLI/RESULT_clap_bart-large-mnli_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/BART-large-MNLI/RESULT_clap_bart-large-mnli_zeroshot.xlsx
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267.4634682079995</v>
+        <v>347.7183233320029</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08915448940266651</v>
+        <v>0.1159061077773343</v>
       </c>
     </row>
   </sheetData>
